--- a/results/final_20260514_v2_summary/Yeast_ScoreVector_summary.xlsx
+++ b/results/final_20260514_v2_summary/Yeast_ScoreVector_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG12"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2429,6 +2429,340 @@
       <c r="AG12" t="inlineStr">
         <is>
           <t>0.1809±0.0053</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ecc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.7256±0.0093</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.6985±0.0116</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.6802±0.0112</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.6508±0.0111</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.8484±0.0053</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.8433±0.0044</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.8371±0.0056</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.8191±0.0056</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.5349±0.0127</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.5128±0.0099</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.4955±0.0071</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.4599±0.0098</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.7240±0.0079</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.7171±0.0077</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.7087±0.0076</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.6845±0.0103</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>6.0794±0.0886</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>6.2340±0.0735</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>6.3880±0.0827</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>6.8072±0.1127</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0.7613±0.0029</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0.7599±0.0040</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0.7567±0.0039</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>0.7432±0.0070</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0.2420±0.0149</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>0.2417±0.0117</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>0.2401±0.0104</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.2406±0.0121</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0.1644±0.0052</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>0.1667±0.0045</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>0.1703±0.0045</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>0.1854±0.0050</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mlknn</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.5998±0.0087</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.5458±0.0111</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.5215±0.0116</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.5178±0.0103</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.7797±0.0043</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.7016±0.0069</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.6551±0.0095</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.6246±0.0102</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.3718±0.0085</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.3285±0.0059</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.3178±0.0075</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0.3136±0.0073</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.6190±0.0125</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.5520±0.0115</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.5146±0.0121</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.4796±0.0144</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>7.3191±0.1087</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>8.8975±0.0953</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>9.7065±0.1623</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>10.0544±0.1515</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0.7029±0.0085</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0.6397±0.0080</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0.6010±0.0119</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0.5689±0.0129</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>0.2665±0.0143</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>0.2716±0.0135</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0.2847±0.0159</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0.3175±0.0227</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>0.2218±0.0078</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>0.2960±0.0068</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0.3461±0.0120</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>0.3770±0.0110</t>
         </is>
       </c>
     </row>
